--- a/data/trans_bre/IP16B06-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B06-Clase-trans_bre.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B06-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B06-Clase-trans_bre.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
